--- a/source/kaoqing/template/出勤状况汇总表.xlsx
+++ b/source/kaoqing/template/出勤状况汇总表.xlsx
@@ -35193,7 +35193,11 @@
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+      <c r="F9" s="206" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
       <c r="G9" s="261"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -35265,7 +35269,9 @@
       <c r="C10" s="37"/>
       <c r="D10" s="37"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="F10" s="206">
+        <v>-3.0</v>
+      </c>
       <c r="G10" s="262"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -35318,11 +35324,19 @@
       <c r="D11" s="150"/>
       <c r="E11" s="150"/>
       <c r="F11" s="150"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="150"/>
+      <c r="G11" s="206">
+        <v>8.5</v>
+      </c>
+      <c r="H11" s="206">
+        <v>8.5</v>
+      </c>
       <c r="I11" s="150"/>
       <c r="J11" s="150"/>
-      <c r="K11" s="150"/>
+      <c r="K11" s="206" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
       <c r="L11" s="150"/>
       <c r="M11" s="150"/>
       <c r="N11" s="150"/>
@@ -35390,11 +35404,13 @@
       <c r="D12" s="151"/>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
-      <c r="G12" s="151"/>
-      <c r="H12" s="151"/>
+      <c r="G12" s="206"/>
+      <c r="H12" s="206"/>
       <c r="I12" s="151"/>
       <c r="J12" s="151"/>
-      <c r="K12" s="151"/>
+      <c r="K12" s="206">
+        <v>-2.0</v>
+      </c>
       <c r="L12" s="151"/>
       <c r="M12" s="151"/>
       <c r="N12" s="151"/>
@@ -35442,8 +35458,12 @@
       <c r="D13" s="11"/>
       <c r="E13" s="150"/>
       <c r="F13" s="150"/>
-      <c r="G13" s="150"/>
-      <c r="H13" s="150"/>
+      <c r="G13" s="206">
+        <v>8.5</v>
+      </c>
+      <c r="H13" s="206">
+        <v>8.5</v>
+      </c>
       <c r="I13" s="150"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
@@ -35514,8 +35534,8 @@
       <c r="D14" s="15"/>
       <c r="E14" s="151"/>
       <c r="F14" s="151"/>
-      <c r="G14" s="151"/>
-      <c r="H14" s="151"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="206"/>
       <c r="I14" s="151"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
@@ -35565,9 +35585,15 @@
       <c r="C15" s="150"/>
       <c r="D15" s="150"/>
       <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
+      <c r="F15" s="206">
+        <v>3.0</v>
+      </c>
+      <c r="G15" s="206">
+        <v>11.5</v>
+      </c>
+      <c r="H15" s="206">
+        <v>11.5</v>
+      </c>
       <c r="I15" s="150"/>
       <c r="J15" s="150"/>
       <c r="K15" s="150"/>
@@ -35637,9 +35663,9 @@
       <c r="C16" s="151"/>
       <c r="D16" s="151"/>
       <c r="E16" s="151"/>
-      <c r="F16" s="151"/>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
+      <c r="F16" s="206"/>
+      <c r="G16" s="206"/>
+      <c r="H16" s="206"/>
       <c r="I16" s="151"/>
       <c r="J16" s="151"/>
       <c r="K16" s="151"/>
@@ -35814,10 +35840,18 @@
       <c r="D19" s="150"/>
       <c r="E19" s="150"/>
       <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="150"/>
+      <c r="G19" s="206">
+        <v>8.5</v>
+      </c>
+      <c r="H19" s="206">
+        <v>8.5</v>
+      </c>
       <c r="I19" s="18"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="206" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
       <c r="K19" s="150"/>
       <c r="L19" s="11"/>
       <c r="M19" s="150"/>
@@ -35886,10 +35920,12 @@
       <c r="D20" s="151"/>
       <c r="E20" s="151"/>
       <c r="F20" s="151"/>
-      <c r="G20" s="151"/>
-      <c r="H20" s="151"/>
+      <c r="G20" s="206"/>
+      <c r="H20" s="206"/>
       <c r="I20" s="50"/>
-      <c r="J20" s="151"/>
+      <c r="J20" s="206">
+        <v>-8.0</v>
+      </c>
       <c r="K20" s="151"/>
       <c r="L20" s="15"/>
       <c r="M20" s="151"/>
@@ -35938,8 +35974,12 @@
       <c r="D21" s="150"/>
       <c r="E21" s="11"/>
       <c r="F21" s="150"/>
-      <c r="G21" s="150"/>
-      <c r="H21" s="150"/>
+      <c r="G21" s="206">
+        <v>8.5</v>
+      </c>
+      <c r="H21" s="206">
+        <v>8.5</v>
+      </c>
       <c r="I21" s="150"/>
       <c r="J21" s="150"/>
       <c r="K21" s="150"/>
@@ -36010,8 +36050,8 @@
       <c r="D22" s="151"/>
       <c r="E22" s="15"/>
       <c r="F22" s="151"/>
-      <c r="G22" s="151"/>
-      <c r="H22" s="151"/>
+      <c r="G22" s="206"/>
+      <c r="H22" s="206"/>
       <c r="I22" s="151"/>
       <c r="J22" s="151"/>
       <c r="K22" s="151"/>
@@ -36063,7 +36103,9 @@
       <c r="E23" s="150"/>
       <c r="F23" s="150"/>
       <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
+      <c r="H23" s="206">
+        <v>8.5</v>
+      </c>
       <c r="I23" s="150"/>
       <c r="J23" s="150"/>
       <c r="K23" s="150"/>
@@ -36135,7 +36177,7 @@
       <c r="E24" s="151"/>
       <c r="F24" s="151"/>
       <c r="G24" s="151"/>
-      <c r="H24" s="151"/>
+      <c r="H24" s="206"/>
       <c r="I24" s="151"/>
       <c r="J24" s="151"/>
       <c r="K24" s="151"/>
@@ -36186,7 +36228,9 @@
       <c r="D25" s="150"/>
       <c r="E25" s="150"/>
       <c r="F25" s="150"/>
-      <c r="G25" s="150"/>
+      <c r="G25" s="206">
+        <v>8.5</v>
+      </c>
       <c r="H25" s="150"/>
       <c r="I25" s="150"/>
       <c r="J25" s="150"/>
@@ -36258,7 +36302,7 @@
       <c r="D26" s="151"/>
       <c r="E26" s="151"/>
       <c r="F26" s="151"/>
-      <c r="G26" s="151"/>
+      <c r="G26" s="206"/>
       <c r="H26" s="151"/>
       <c r="I26" s="151"/>
       <c r="J26" s="151"/>
@@ -36433,9 +36477,15 @@
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="F29" s="206">
+        <v>3.0</v>
+      </c>
+      <c r="G29" s="206">
+        <v>11.5</v>
+      </c>
+      <c r="H29" s="206">
+        <v>11.5</v>
+      </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -36505,9 +36555,9 @@
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="F30" s="206"/>
+      <c r="G30" s="206"/>
+      <c r="H30" s="206"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
@@ -36682,7 +36732,7 @@
       <c r="AH33" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="340">
+  <mergeCells count="341">
     <mergeCell ref="AK29:AK30"/>
     <mergeCell ref="AL29:AL30"/>
     <mergeCell ref="AP29:AP30"/>
@@ -36840,7 +36890,6 @@
     <mergeCell ref="T19:T20"/>
     <mergeCell ref="U19:U20"/>
     <mergeCell ref="H19:H20"/>
-    <mergeCell ref="J19:J20"/>
     <mergeCell ref="K19:K20"/>
     <mergeCell ref="M19:M20"/>
     <mergeCell ref="N19:N20"/>
@@ -36970,7 +37019,6 @@
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="A11:A12"/>
@@ -37023,6 +37071,9 @@
     <mergeCell ref="AQ2:AQ4"/>
     <mergeCell ref="AH3:AL3"/>
     <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="C3:AG30">
